--- a/artfynd/A 33778-2026 artfynd.xlsx
+++ b/artfynd/A 33778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395753</v>
       </c>
       <c r="B2" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33778-2026 artfynd.xlsx
+++ b/artfynd/A 33778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395753</v>
       </c>
       <c r="B2" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33778-2026 artfynd.xlsx
+++ b/artfynd/A 33778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395753</v>
       </c>
       <c r="B2" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33778-2026 artfynd.xlsx
+++ b/artfynd/A 33778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137395753</v>
       </c>
       <c r="B2" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137395642</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137395772</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
